--- a/hourly datasets/cap_gen_year0final.xlsx
+++ b/hourly datasets/cap_gen_year0final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1089366021538427</v>
+        <v>0.1053128620452669</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08500062045203191</v>
+        <v>0.08077640411357627</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1939372226058746</v>
+        <v>0.1860892661588431</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09917304706097013</v>
+        <v>0.09499552086174223</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.2081096492148129</v>
+        <v>0.2003083829070091</v>
       </c>
     </row>
     <row r="5">
@@ -531,25 +531,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.123807232963945</v>
+        <v>0.1117620579893327</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01369461941555491</v>
+        <v>0.0113784010784643</v>
       </c>
       <c r="D5" t="n">
-        <v>16.00202245006286</v>
+        <v>14.95694067647882</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06129388298243208</v>
+        <v>0.04871068823501443</v>
       </c>
       <c r="F5" t="n">
-        <v>0.09691080096350797</v>
+        <v>0.08942645812876338</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1507036649643816</v>
+        <v>0.134097657849903</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2327438351177878</v>
+        <v>0.2170749200345996</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1110720067567618</v>
+        <v>0.09424162299854899</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -567,7 +567,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.2200086089106045</v>
+        <v>0.1995544850438159</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03698560271094231</v>
+        <v>0.02845327147436652</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -585,7 +585,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.145922204864785</v>
+        <v>0.1337661335196334</v>
       </c>
     </row>
     <row r="8">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03114616664858009</v>
+        <v>0.02279739793769568</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -603,7 +603,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>0.1400827688024228</v>
+        <v>0.1281102599829625</v>
       </c>
     </row>
     <row r="9">
@@ -613,25 +613,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01659237862443653</v>
+        <v>0.005848597596317996</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002386670275222697</v>
+        <v>0.0007811245376902163</v>
       </c>
       <c r="D9" t="n">
-        <v>1.346453958426267</v>
+        <v>0.6350435654048943</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01391397053886815</v>
+        <v>0.01353257655409514</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01187945893565428</v>
+        <v>0.004314591955491918</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02130529831321876</v>
+        <v>0.007382603237144096</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1255289807782793</v>
+        <v>0.1111614596415849</v>
       </c>
     </row>
     <row r="10">
@@ -641,25 +641,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.01571141166047701</v>
+        <v>0.005617132983226362</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001858316576873916</v>
+        <v>0.0005500787079465345</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9755545145950986</v>
+        <v>0.4896827684215669</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003225062826648291</v>
+        <v>0.006030982577198886</v>
       </c>
       <c r="F10" t="n">
-        <v>0.01205509558667424</v>
+        <v>0.004536187727581321</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01936772773428012</v>
+        <v>0.006698078238871454</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1246480138143198</v>
+        <v>0.1109299950284932</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02662391629174165</v>
+        <v>0.02513797826394039</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -677,7 +677,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1355605184455844</v>
+        <v>0.1304508403092073</v>
       </c>
     </row>
     <row r="12">
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.038878014885981</v>
+        <v>0.03741241792251303</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -695,7 +695,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1478146170398237</v>
+        <v>0.1427252799677799</v>
       </c>
     </row>
     <row r="13">
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05065715289869716</v>
+        <v>0.04856017620174218</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -713,7 +713,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1595937550525399</v>
+        <v>0.153873038247009</v>
       </c>
     </row>
     <row r="14">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05419193279007294</v>
+        <v>0.05236921512246992</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -731,7 +731,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1631285349439157</v>
+        <v>0.1576820771677368</v>
       </c>
     </row>
     <row r="15">
@@ -741,25 +741,15 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05995336894647041</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.008943036960297145</v>
-      </c>
-      <c r="D15" t="n">
-        <v>11.68031312222276</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.04716771729463884</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.04239731264739489</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.07750942524554597</v>
-      </c>
+        <v>0.05798942519929258</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1688899711003131</v>
+        <v>0.1633022872445595</v>
       </c>
     </row>
     <row r="16">
@@ -769,7 +759,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.0642453643400073</v>
+        <v>0.06304096635446546</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -777,7 +767,7 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.17318196649385</v>
+        <v>0.1683538283997323</v>
       </c>
     </row>
     <row r="17">
@@ -787,25 +777,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.06825029440056077</v>
+        <v>0.06659062268313154</v>
       </c>
       <c r="C17" t="n">
-        <v>0.008841851205278278</v>
+        <v>0.008060248939608983</v>
       </c>
       <c r="D17" t="n">
-        <v>12.66402477271134</v>
+        <v>13.15528108474331</v>
       </c>
       <c r="E17" t="n">
-        <v>0.05173022530280881</v>
+        <v>0.0525475036996231</v>
       </c>
       <c r="F17" t="n">
-        <v>0.05089728137956876</v>
+        <v>0.05077785350965034</v>
       </c>
       <c r="G17" t="n">
-        <v>0.08560330742155288</v>
+        <v>0.08240339185661279</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1771868965544035</v>
+        <v>0.1719034847283984</v>
       </c>
     </row>
     <row r="18">
@@ -815,22 +805,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1089366021538427</v>
+        <v>-0.1053128620452669</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01281683042101939</v>
+        <v>0.01211968401275546</v>
       </c>
       <c r="D18" t="n">
-        <v>-16.44676351054337</v>
+        <v>-16.4060812491125</v>
       </c>
       <c r="E18" t="n">
-        <v>0.04008260604847166</v>
+        <v>0.04643115550599784</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1341034378989942</v>
+        <v>-0.1290960224197218</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08376976640869119</v>
+        <v>-0.08152970167081175</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -843,7 +833,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.06830557377428821</v>
+        <v>0.06662718327537329</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -851,7 +841,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.177242175928131</v>
+        <v>0.1719400453206402</v>
       </c>
     </row>
     <row r="20">
@@ -861,25 +851,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.07226336649908023</v>
+        <v>0.06985566160357162</v>
       </c>
       <c r="C20" t="n">
-        <v>0.00890602765187856</v>
+        <v>0.00804147680392758</v>
       </c>
       <c r="D20" t="n">
-        <v>5668150894494.086</v>
+        <v>6242647634423.186</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04432099779570591</v>
+        <v>0.04435006454794617</v>
       </c>
       <c r="F20" t="n">
-        <v>0.05478289827742396</v>
+        <v>0.05407812041861603</v>
       </c>
       <c r="G20" t="n">
-        <v>0.08974383472073651</v>
+        <v>0.08563320278852724</v>
       </c>
       <c r="H20" t="n">
-        <v>0.181199968652923</v>
+        <v>0.1751685236488385</v>
       </c>
     </row>
     <row r="21">
@@ -889,25 +879,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.07241528648047106</v>
+        <v>0.07050745302533212</v>
       </c>
       <c r="C21" t="n">
-        <v>0.008991318092873422</v>
+        <v>0.008387624765873231</v>
       </c>
       <c r="D21" t="n">
-        <v>-428133630578.8991</v>
+        <v>-400808518264.1587</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0506141623508175</v>
+        <v>0.05262870125636104</v>
       </c>
       <c r="F21" t="n">
-        <v>0.05476696315514627</v>
+        <v>0.05404810831924279</v>
       </c>
       <c r="G21" t="n">
-        <v>0.09006360980579604</v>
+        <v>0.0869667977314216</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1813518886343138</v>
+        <v>0.175820315070599</v>
       </c>
     </row>
     <row r="22">
@@ -917,25 +907,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0729059892368354</v>
+        <v>0.07268680789973231</v>
       </c>
       <c r="C22" t="n">
-        <v>0.008834673550572545</v>
+        <v>0.008257185041885698</v>
       </c>
       <c r="D22" t="n">
-        <v>104298678.5056185</v>
+        <v>98440399.23951316</v>
       </c>
       <c r="E22" t="n">
-        <v>0.05542860158423735</v>
+        <v>0.05313017213826348</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0555645292479386</v>
+        <v>0.0564859587384075</v>
       </c>
       <c r="G22" t="n">
-        <v>0.09024744922573248</v>
+        <v>0.08888765706105725</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1818425913906782</v>
+        <v>0.1779996699449992</v>
       </c>
     </row>
     <row r="23">
@@ -945,25 +935,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0738015138916179</v>
+        <v>0.07261108541608975</v>
       </c>
       <c r="C23" t="n">
-        <v>0.00887600175227507</v>
+        <v>0.008328332976192385</v>
       </c>
       <c r="D23" t="n">
-        <v>609921337538.8508</v>
+        <v>575764509599.5231</v>
       </c>
       <c r="E23" t="n">
-        <v>0.05043224462281864</v>
+        <v>0.0500008274869668</v>
       </c>
       <c r="F23" t="n">
-        <v>0.05637587448914926</v>
+        <v>0.05627179714722421</v>
       </c>
       <c r="G23" t="n">
-        <v>0.09122715329408662</v>
+        <v>0.08895037368495531</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1827381160454606</v>
+        <v>0.1779239474613566</v>
       </c>
     </row>
     <row r="24">
@@ -973,25 +963,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.07547225321043659</v>
+        <v>0.07526735010653957</v>
       </c>
       <c r="C24" t="n">
-        <v>0.008532349552489216</v>
+        <v>0.008108316043961094</v>
       </c>
       <c r="D24" t="n">
-        <v>531793911756.0118</v>
+        <v>506548734792.8252</v>
       </c>
       <c r="E24" t="n">
-        <v>0.05373465134791208</v>
+        <v>0.05655511449591177</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05872494904565367</v>
+        <v>0.05935986418147814</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0922195573752197</v>
+        <v>0.09117483603160108</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1844088553642793</v>
+        <v>0.1805802121518064</v>
       </c>
     </row>
     <row r="25">
@@ -1001,25 +991,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.07771443315715504</v>
+        <v>0.07519807099646743</v>
       </c>
       <c r="C25" t="n">
-        <v>0.009112689933835834</v>
+        <v>0.008292707630820949</v>
       </c>
       <c r="D25" t="n">
-        <v>6634860042354.429</v>
+        <v>6224688291751.375</v>
       </c>
       <c r="E25" t="n">
-        <v>0.06172046840013464</v>
+        <v>0.0614539695515236</v>
       </c>
       <c r="F25" t="n">
-        <v>0.05982240874266918</v>
+        <v>0.05893028390180971</v>
       </c>
       <c r="G25" t="n">
-        <v>0.09560645757164075</v>
+        <v>0.09146585809112487</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1866510353109978</v>
+        <v>0.1805109330417343</v>
       </c>
     </row>
     <row r="26">
@@ -1029,25 +1019,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.08000025974785395</v>
+        <v>0.07675969907696219</v>
       </c>
       <c r="C26" t="n">
-        <v>0.009167721000248905</v>
+        <v>0.00861749152975193</v>
       </c>
       <c r="D26" t="n">
-        <v>12.72034225711517</v>
+        <v>12.83693754195008</v>
       </c>
       <c r="E26" t="n">
-        <v>0.05365001257679801</v>
+        <v>0.05392597095024815</v>
       </c>
       <c r="F26" t="n">
-        <v>0.06200389481192491</v>
+        <v>0.05985152158096869</v>
       </c>
       <c r="G26" t="n">
-        <v>0.09799662468378292</v>
+        <v>0.09366787657295564</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1889368619016967</v>
+        <v>0.1820725611222291</v>
       </c>
     </row>
     <row r="27">
@@ -1057,25 +1047,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.07900893735709619</v>
+        <v>0.07574033417872698</v>
       </c>
       <c r="C27" t="n">
-        <v>0.009556243819865662</v>
+        <v>0.008778549271945392</v>
       </c>
       <c r="D27" t="n">
-        <v>12.45274135783254</v>
+        <v>1091008235764.807</v>
       </c>
       <c r="E27" t="n">
-        <v>0.05898925413476505</v>
+        <v>0.05569515774110703</v>
       </c>
       <c r="F27" t="n">
-        <v>0.06024596718288395</v>
+        <v>0.05851763599868937</v>
       </c>
       <c r="G27" t="n">
-        <v>0.09777190753130867</v>
+        <v>0.09296303235876445</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1879455395109389</v>
+        <v>0.1810531962239939</v>
       </c>
     </row>
     <row r="28">
@@ -1085,25 +1075,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.08342092917406124</v>
+        <v>0.07881343664927067</v>
       </c>
       <c r="C28" t="n">
-        <v>0.009432738458176711</v>
+        <v>0.009033893944576035</v>
       </c>
       <c r="D28" t="n">
-        <v>12.37454337021428</v>
+        <v>12.54071312434027</v>
       </c>
       <c r="E28" t="n">
-        <v>0.06874796859422674</v>
+        <v>0.06838126769451451</v>
       </c>
       <c r="F28" t="n">
-        <v>0.06491092979499977</v>
+        <v>0.06108787866391218</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1019309285531226</v>
+        <v>0.09653899463462887</v>
       </c>
       <c r="H28" t="n">
-        <v>0.192357531327904</v>
+        <v>0.1841262986945376</v>
       </c>
     </row>
     <row r="29">
@@ -1113,25 +1103,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.008933096119192879</v>
+        <v>0.007497814878019061</v>
       </c>
       <c r="C29" t="n">
-        <v>0.003874225444742033</v>
+        <v>0.0004930524031261776</v>
       </c>
       <c r="D29" t="n">
-        <v>1.163037890108816</v>
+        <v>0.9474595015217098</v>
       </c>
       <c r="E29" t="n">
-        <v>0.03203492588249782</v>
+        <v>0.006596687632565988</v>
       </c>
       <c r="F29" t="n">
-        <v>0.001305982207810635</v>
+        <v>0.00652978210621831</v>
       </c>
       <c r="G29" t="n">
-        <v>0.01656021003057486</v>
+        <v>0.008465847649819868</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1178696982730356</v>
+        <v>0.1128106769232859</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year0final.xlsx
+++ b/hourly datasets/cap_gen_year0final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2290188973710566</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1053128620452669</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1024392042946382</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08077640411357627</v>
+        <v>0.3374743754122724</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1860892661588431</v>
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.210894682335854</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +524,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09499552086174223</v>
+        <v>0.3409618055577103</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +532,10 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.2003083829070091</v>
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.2143821124812919</v>
       </c>
     </row>
     <row r="5">
@@ -531,25 +545,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1117620579893327</v>
+        <v>0.3439125913514464</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0113784010784643</v>
+        <v>0.01230210125477235</v>
       </c>
       <c r="D5" t="n">
-        <v>14.95694067647882</v>
+        <v>16.31948590615999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04871068823501443</v>
+        <v>0.04936607022387256</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08942645812876338</v>
+        <v>0.1009468654756843</v>
       </c>
       <c r="G5" t="n">
-        <v>0.134097657849903</v>
+        <v>0.1492406050770356</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2170749200345996</v>
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.217332898275028</v>
       </c>
     </row>
     <row r="6">
@@ -559,7 +576,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.09424162299854899</v>
+        <v>0.3567347778315152</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
@@ -567,7 +584,10 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
-        <v>0.1995544850438159</v>
+        <v>4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2301550847550968</v>
       </c>
     </row>
     <row r="7">
@@ -577,7 +597,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02845327147436652</v>
+        <v>0.3268075836840088</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -585,7 +605,10 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>0.1337661335196334</v>
+        <v>29</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.2002278906075903</v>
       </c>
     </row>
     <row r="8">
@@ -595,7 +618,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02279739793769568</v>
+        <v>0.3303944404341491</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -603,7 +626,10 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>0.1281102599829625</v>
+        <v>29</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.2038147473577307</v>
       </c>
     </row>
     <row r="9">
@@ -613,25 +639,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.005848597596317996</v>
+        <v>0.281531200847522</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0007811245376902163</v>
+        <v>0.002625723210069993</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6350435654048943</v>
+        <v>2.171935062069105</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01353257655409514</v>
+        <v>0.06234551064990347</v>
       </c>
       <c r="F9" t="n">
-        <v>0.004314591955491918</v>
+        <v>-0.0006304786291604737</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007382603237144096</v>
+        <v>0.009683153433914108</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1111614596415849</v>
+        <v>67</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1549515077711036</v>
       </c>
     </row>
     <row r="10">
@@ -641,25 +670,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.005617132983226362</v>
+        <v>0.2872079299127576</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0005500787079465345</v>
+        <v>0.001739853907311601</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4896827684215669</v>
+        <v>2.19121595926002</v>
       </c>
       <c r="E10" t="n">
-        <v>0.006030982577198886</v>
+        <v>0.08334599354413365</v>
       </c>
       <c r="F10" t="n">
-        <v>0.004536187727581321</v>
+        <v>0.00540174449011719</v>
       </c>
       <c r="G10" t="n">
-        <v>0.006698078238871454</v>
+        <v>0.01223079366214746</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1109299950284932</v>
+        <v>67</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1606282368363391</v>
       </c>
     </row>
     <row r="11">
@@ -669,7 +701,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02513797826394039</v>
+        <v>0.2632245693860752</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -677,7 +709,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1304508403092073</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1366448763096568</v>
       </c>
     </row>
     <row r="12">
@@ -687,7 +722,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03741241792251303</v>
+        <v>0.2802004577659439</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -695,7 +730,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1427252799677799</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1536207646895255</v>
       </c>
     </row>
     <row r="13">
@@ -705,7 +743,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04856017620174218</v>
+        <v>0.291956460562256</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -713,7 +751,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.153873038247009</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1653767674858376</v>
       </c>
     </row>
     <row r="14">
@@ -723,7 +764,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05236921512246992</v>
+        <v>0.3010451348533713</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -731,7 +772,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1576820771677368</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1744654417769529</v>
       </c>
     </row>
     <row r="15">
@@ -741,7 +785,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05798942519929258</v>
+        <v>0.3083584694505939</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -749,7 +793,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1633022872445595</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1817787763741754</v>
       </c>
     </row>
     <row r="16">
@@ -759,7 +806,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.06304096635446546</v>
+        <v>0.3143091246728399</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
@@ -767,7 +814,10 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>0.1683538283997323</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1877294315964215</v>
       </c>
     </row>
     <row r="17">
@@ -777,25 +827,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.06659062268313154</v>
+        <v>0.3183660714896628</v>
       </c>
       <c r="C17" t="n">
-        <v>0.008060248939608983</v>
+        <v>0.008053363185516634</v>
       </c>
       <c r="D17" t="n">
-        <v>13.15528108474331</v>
+        <v>13.14529963597951</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0525475036996231</v>
+        <v>0.05250686777340922</v>
       </c>
       <c r="F17" t="n">
-        <v>0.05077785350965034</v>
+        <v>0.05072668874235695</v>
       </c>
       <c r="G17" t="n">
-        <v>0.08240339185661279</v>
+        <v>0.08232520849205914</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1719034847283984</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1917863784132444</v>
       </c>
     </row>
     <row r="18">
@@ -805,24 +858,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1053128620452669</v>
+        <v>0.1265796930764184</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01211968401275546</v>
+        <v>0.01206897350709684</v>
       </c>
       <c r="D18" t="n">
-        <v>-16.4060812491125</v>
+        <v>-16.35095512590432</v>
       </c>
       <c r="E18" t="n">
-        <v>0.04643115550599784</v>
+        <v>0.04563258587427248</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1290960224197218</v>
+        <v>-0.1286127973772164</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08152970167081175</v>
+        <v>-0.0812455116062214</v>
       </c>
       <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -833,7 +889,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.06662718327537329</v>
+        <v>0.3187522011407609</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
@@ -841,7 +897,10 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>0.1719400453206402</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.1921725080643425</v>
       </c>
     </row>
     <row r="20">
@@ -851,25 +910,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.06985566160357162</v>
+        <v>0.3222534036658257</v>
       </c>
       <c r="C20" t="n">
-        <v>0.00804147680392758</v>
+        <v>0.008052997544334353</v>
       </c>
       <c r="D20" t="n">
-        <v>6242647634423.186</v>
+        <v>6251591255675.94</v>
       </c>
       <c r="E20" t="n">
-        <v>0.04435006454794617</v>
+        <v>0.04441360332237016</v>
       </c>
       <c r="F20" t="n">
-        <v>0.05407812041861603</v>
+        <v>0.05415559623583468</v>
       </c>
       <c r="G20" t="n">
-        <v>0.08563320278852724</v>
+        <v>0.08575588646014404</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1751685236488385</v>
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.1956737105894072</v>
       </c>
     </row>
     <row r="21">
@@ -879,25 +941,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.07050745302533212</v>
+        <v>0.3237485940244146</v>
       </c>
       <c r="C21" t="n">
-        <v>0.008387624765873231</v>
+        <v>0.008399641420265599</v>
       </c>
       <c r="D21" t="n">
-        <v>-400808518264.1587</v>
+        <v>-401382742502.3594</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05262870125636104</v>
+        <v>0.05270410054182861</v>
       </c>
       <c r="F21" t="n">
-        <v>0.05404810831924279</v>
+        <v>0.0541255411391844</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0869667977314216</v>
+        <v>0.08709139199751247</v>
       </c>
       <c r="H21" t="n">
-        <v>0.175820315070599</v>
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.1971689009479962</v>
       </c>
     </row>
     <row r="22">
@@ -907,25 +972,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.07268680789973231</v>
+        <v>0.3260570843642731</v>
       </c>
       <c r="C22" t="n">
-        <v>0.008257185041885698</v>
+        <v>0.008269014819882669</v>
       </c>
       <c r="D22" t="n">
-        <v>98440399.23951316</v>
+        <v>98581431.33011417</v>
       </c>
       <c r="E22" t="n">
-        <v>0.05313017213826348</v>
+        <v>0.05320628986338993</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0564859587384075</v>
+        <v>0.05656688418072614</v>
       </c>
       <c r="G22" t="n">
-        <v>0.08888765706105725</v>
+        <v>0.08901500327461177</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1779996699449992</v>
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.1994773912878547</v>
       </c>
     </row>
     <row r="23">
@@ -935,25 +1003,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.07261108541608975</v>
+        <v>0.3272520376166899</v>
       </c>
       <c r="C23" t="n">
-        <v>0.008328332976192385</v>
+        <v>0.008340264685327331</v>
       </c>
       <c r="D23" t="n">
-        <v>575764509599.5231</v>
+        <v>576589387120.4393</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0500008274869668</v>
+        <v>0.05007246191030056</v>
       </c>
       <c r="F23" t="n">
-        <v>0.05627179714722421</v>
+        <v>0.05635241576777898</v>
       </c>
       <c r="G23" t="n">
-        <v>0.08895037368495531</v>
+        <v>0.08907780975040655</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1779239474613566</v>
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2006723445402714</v>
       </c>
     </row>
     <row r="24">
@@ -963,25 +1034,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.07526735010653957</v>
+        <v>0.3299355228772223</v>
       </c>
       <c r="C24" t="n">
-        <v>0.008108316043961094</v>
+        <v>0.008119932542591411</v>
       </c>
       <c r="D24" t="n">
-        <v>506548734792.8252</v>
+        <v>507274449312.5857</v>
       </c>
       <c r="E24" t="n">
-        <v>0.05655511449591177</v>
+        <v>0.05663613901524689</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05935986418147814</v>
+        <v>0.05944490696683842</v>
       </c>
       <c r="G24" t="n">
-        <v>0.09117483603160108</v>
+        <v>0.09130545900585839</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1805802121518064</v>
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2033558298008039</v>
       </c>
     </row>
     <row r="25">
@@ -991,25 +1065,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.07519807099646743</v>
+        <v>0.3310046612861492</v>
       </c>
       <c r="C25" t="n">
-        <v>0.008292707630820949</v>
+        <v>0.008304588300779145</v>
       </c>
       <c r="D25" t="n">
-        <v>6224688291751.375</v>
+        <v>6233606183286.835</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0614539695515236</v>
+        <v>0.06154201248784383</v>
       </c>
       <c r="F25" t="n">
-        <v>0.05893028390180971</v>
+        <v>0.05901471124264325</v>
       </c>
       <c r="G25" t="n">
-        <v>0.09146585809112487</v>
+        <v>0.0915968980024302</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1805109330417343</v>
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2044249682097308</v>
       </c>
     </row>
     <row r="26">
@@ -1019,25 +1096,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.07675969907696219</v>
+        <v>0.3337239265010305</v>
       </c>
       <c r="C26" t="n">
-        <v>0.00861749152975193</v>
+        <v>0.008629837506155586</v>
       </c>
       <c r="D26" t="n">
-        <v>12.83693754195008</v>
+        <v>12.85532856994715</v>
       </c>
       <c r="E26" t="n">
-        <v>0.05392597095024815</v>
+        <v>0.05400322878828575</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05985152158096869</v>
+        <v>0.05993726874655747</v>
       </c>
       <c r="G26" t="n">
-        <v>0.09366787657295564</v>
+        <v>0.09380207123853293</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1820725611222291</v>
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.2071442334246121</v>
       </c>
     </row>
     <row r="27">
@@ -1047,25 +1127,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.07574033417872698</v>
+        <v>0.3339542217465679</v>
       </c>
       <c r="C27" t="n">
-        <v>0.008778549271945392</v>
+        <v>0.00879112599010004</v>
       </c>
       <c r="D27" t="n">
-        <v>1091008235764.807</v>
+        <v>1092571284813.181</v>
       </c>
       <c r="E27" t="n">
-        <v>0.05569515774110703</v>
+        <v>0.05577495023070746</v>
       </c>
       <c r="F27" t="n">
-        <v>0.05851763599868937</v>
+        <v>0.05860147215341529</v>
       </c>
       <c r="G27" t="n">
-        <v>0.09296303235876445</v>
+        <v>0.09309621721887729</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1810531962239939</v>
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.2073745286701494</v>
       </c>
     </row>
     <row r="28">
@@ -1075,25 +1158,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.07881343664927067</v>
+        <v>0.3365782704741977</v>
       </c>
       <c r="C28" t="n">
-        <v>0.009033893944576035</v>
+        <v>0.009046836486043909</v>
       </c>
       <c r="D28" t="n">
-        <v>12.54071312434027</v>
+        <v>12.55867976205422</v>
       </c>
       <c r="E28" t="n">
-        <v>0.06838126769451451</v>
+        <v>0.06847923512674162</v>
       </c>
       <c r="F28" t="n">
-        <v>0.06108787866391218</v>
+        <v>0.06117539711472007</v>
       </c>
       <c r="G28" t="n">
-        <v>0.09653899463462887</v>
+        <v>0.09667730264986472</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1841262986945376</v>
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2099985773977793</v>
       </c>
     </row>
     <row r="29">
@@ -1103,25 +1189,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.007497814878019061</v>
+        <v>0.2865914729046057</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0004930524031261776</v>
+        <v>0.001182880613561103</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9474595015217098</v>
+        <v>4.659632098096481</v>
       </c>
       <c r="E29" t="n">
-        <v>0.006596687632565988</v>
+        <v>0.03459715660260396</v>
       </c>
       <c r="F29" t="n">
-        <v>0.00652978210621831</v>
+        <v>0.008641593556533416</v>
       </c>
       <c r="G29" t="n">
-        <v>0.008465847649819868</v>
+        <v>0.013283404158573</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1128106769232859</v>
+        <v>67</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.1600117798281873</v>
       </c>
     </row>
   </sheetData>
